--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\motifoye\Desktop\map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F962E379-CD79-452D-893A-5C81D1F4164A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14EE403-6F0D-4E51-8117-6B109A96A48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3690" yWindow="4695" windowWidth="21600" windowHeight="11505" xr2:uid="{67BA941E-2A1D-48F0-9EB1-F75B5C4F512E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t xml:space="preserve">название места </t>
   </si>
@@ -76,6 +76,15 @@
   </si>
   <si>
     <t>категория</t>
+  </si>
+  <si>
+    <t>Места посадки человека</t>
+  </si>
+  <si>
+    <t>Места посадки автоматических зондов</t>
+  </si>
+  <si>
+    <t>Географические достопримечательности</t>
   </si>
 </sst>
 </file>
@@ -435,7 +444,8 @@
     <col min="2" max="3" width="19.42578125" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="13.140625" customWidth="1"/>
-    <col min="6" max="7" width="10.140625" customWidth="1"/>
+    <col min="6" max="6" width="39.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -474,8 +484,8 @@
       <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="F2">
-        <v>1</v>
+      <c r="F2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -494,8 +504,8 @@
       <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="F3">
-        <v>2</v>
+      <c r="F3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -514,8 +524,8 @@
       <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="F4">
-        <v>3</v>
+      <c r="F4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\motifoye\Desktop\map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14EE403-6F0D-4E51-8117-6B109A96A48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1427FBEB-28F6-4763-BCBF-C62CA1119BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3690" yWindow="4695" windowWidth="21600" windowHeight="11505" xr2:uid="{67BA941E-2A1D-48F0-9EB1-F75B5C4F512E}"/>
+    <workbookView xWindow="2565" yWindow="7665" windowWidth="21600" windowHeight="11505" xr2:uid="{67BA941E-2A1D-48F0-9EB1-F75B5C4F512E}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t xml:space="preserve">название места </t>
   </si>
@@ -54,27 +54,15 @@
     <t>маркер места</t>
   </si>
   <si>
-    <t>150;500</t>
-  </si>
-  <si>
     <t>op.webp</t>
   </si>
   <si>
-    <t>описание</t>
-  </si>
-  <si>
     <t>название</t>
   </si>
   <si>
     <t>marker.png</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1000;100</t>
-  </si>
-  <si>
-    <t>300;600</t>
-  </si>
-  <si>
     <t>категория</t>
   </si>
   <si>
@@ -85,6 +73,36 @@
   </si>
   <si>
     <t>Географические достопримечательности</t>
+  </si>
+  <si>
+    <t>описвыаыаыа</t>
+  </si>
+  <si>
+    <t>ыы4432кцм</t>
+  </si>
+  <si>
+    <t>оп34242ыаыаы</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1000;1000</t>
+  </si>
+  <si>
+    <t>150;1500</t>
+  </si>
+  <si>
+    <t>1110;600</t>
+  </si>
+  <si>
+    <t>i.webp</t>
+  </si>
+  <si>
+    <t>y.webp</t>
+  </si>
+  <si>
+    <t>7.webp</t>
+  </si>
+  <si>
+    <t>u.webp</t>
   </si>
 </sst>
 </file>
@@ -465,67 +483,67 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\motifoye\Desktop\map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1427FBEB-28F6-4763-BCBF-C62CA1119BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CCF0B2-9394-4F92-B067-FFBC15F1278C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="7665" windowWidth="21600" windowHeight="11505" xr2:uid="{67BA941E-2A1D-48F0-9EB1-F75B5C4F512E}"/>
+    <workbookView xWindow="6180" yWindow="2880" windowWidth="21600" windowHeight="11505" xr2:uid="{67BA941E-2A1D-48F0-9EB1-F75B5C4F512E}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -87,9 +87,6 @@
     <t xml:space="preserve"> 1000;1000</t>
   </si>
   <si>
-    <t>150;1500</t>
-  </si>
-  <si>
     <t>1110;600</t>
   </si>
   <si>
@@ -103,6 +100,9 @@
   </si>
   <si>
     <t>u.webp</t>
+  </si>
+  <si>
+    <t>150;800</t>
   </si>
 </sst>
 </file>
@@ -494,13 +494,13 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -511,16 +511,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
@@ -531,7 +531,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\motifoye\Desktop\map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CCF0B2-9394-4F92-B067-FFBC15F1278C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89068DBC-EB07-4E04-88F9-D824A4A35DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6180" yWindow="2880" windowWidth="21600" windowHeight="11505" xr2:uid="{67BA941E-2A1D-48F0-9EB1-F75B5C4F512E}"/>
+    <workbookView xWindow="7455" yWindow="3270" windowWidth="21600" windowHeight="11505" xr2:uid="{67BA941E-2A1D-48F0-9EB1-F75B5C4F512E}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">название места </t>
   </si>
@@ -54,15 +54,6 @@
     <t>маркер места</t>
   </si>
   <si>
-    <t>op.webp</t>
-  </si>
-  <si>
-    <t>название</t>
-  </si>
-  <si>
-    <t>marker.png</t>
-  </si>
-  <si>
     <t>категория</t>
   </si>
   <si>
@@ -75,34 +66,49 @@
     <t>Географические достопримечательности</t>
   </si>
   <si>
-    <t>описвыаыаыа</t>
-  </si>
-  <si>
-    <t>ыы4432кцм</t>
-  </si>
-  <si>
-    <t>оп34242ыаыаы</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1000;1000</t>
-  </si>
-  <si>
-    <t>1110;600</t>
-  </si>
-  <si>
-    <t>i.webp</t>
-  </si>
-  <si>
-    <t>y.webp</t>
-  </si>
-  <si>
-    <t>7.webp</t>
-  </si>
-  <si>
-    <t>u.webp</t>
-  </si>
-  <si>
-    <t>150;800</t>
+    <t xml:space="preserve"> 1160;510</t>
+  </si>
+  <si>
+    <t>ap11.jpg</t>
+  </si>
+  <si>
+    <t>Аполлон-11 — американский пилотируемый космический корабль серии «Аполлон», в ходе полёта которого 16—24 июля 1969 года люди впервые в истории совершили посадку на поверхность Луны. 20 июля 1969 года в 20:17:39 UTC командир экипажа Нил Армстронг и пилот Эдвин Олдрин посадили лунный модуль корабля в юго-западном районе Моря Спокойствия. Время пребывания на лунной поверхности составило 21 час 36 минут 21 секунду. Пилот командного модуля Майкл Коллинз всё это время находился на окололунной орбите. Первым человеком, ступившим на Луну, стал Нил Армстронг — это произошло 21 июля в 02:56:15 UTC. Через 15 минут к нему присоединился Олдрин. Астронавты установили в месте посадки флаг США, разместили комплект научных приборов и собрали 21,55 кг образцов лунного грунта, которые были доставлены на Землю. После полёта члены экипажа и образцы лунной породы прошли строгий карантин, не выявивший наличия каких-либо лунных микроорганизмов.</t>
+  </si>
+  <si>
+    <t>mk1.webp</t>
+  </si>
+  <si>
+    <t>Аполлон-11</t>
+  </si>
+  <si>
+    <t>1020;350</t>
+  </si>
+  <si>
+    <t>Луна-2</t>
+  </si>
+  <si>
+    <t>Луна-2 — вторая советская автоматическая межпланетная станция, первая в мире станция, достигшая поверхности Луны. Это второй аппарат советской космической программы «Луна». 12 сентября 1959 года в 10:39:42 по московскому времени осуществлён пуск ракеты-носителя «Восток-Л», которая вывела станцию на траекторию полёта к Луне. 14 сентября 1959 года в 00:02:24 станция «Луна-2» впервые в мире достигла поверхности Луны в районе Моря Дождей вблизи кратеров Аристилл, Архимед и Автолик</t>
+  </si>
+  <si>
+    <t>mk2.webp</t>
+  </si>
+  <si>
+    <t>mn2.webp</t>
+  </si>
+  <si>
+    <t>1091;350</t>
+  </si>
+  <si>
+    <t>Кратер Линней</t>
+  </si>
+  <si>
+    <t>Кратер Линней — небольшой сравнительно молодой ударный кратер в северо-западной части Моря Ясности на видимой стороне Луны. Кратер назван в честь Карла Линнея (1707—1778), выдающегося шведского естествоиспытателя и медика. Ближайшими соседями кратера являются кратер Сантос-Дюмон, кратер Хорнсби. На северо-западе от кратера находятся горы Кавказ и за ними Море Дождей. Диаметр кратера 2,23 км, глубина 600 м. Кратер Линней образован в толще базальтовых пород Моря Спокойствия и имеет усечённую конусообразную форму. Вал с чётко очерченной острой кромкой, окружён дюнообразной областью пород с высоким альбедо, выброшенных при образовании кратера. Внутренний склон гладкий, с радиальными полосами по всему периметру. Кратер Линней относится к числу кратеров, в которых зарегистрированы температурные аномалии во время затмений. Это объясняется тем, что подобные кратеры имеют небольшой возраст и скалы не успели покрыться реголитом, оказывающим термоизолирующее действие.</t>
+  </si>
+  <si>
+    <t>mk3.png</t>
+  </si>
+  <si>
+    <t>krL.png</t>
   </si>
 </sst>
 </file>
@@ -483,67 +489,67 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\motifoye\Desktop\map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89068DBC-EB07-4E04-88F9-D824A4A35DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762B366F-F83B-47EC-B13A-53F3F66D9F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7455" yWindow="3270" windowWidth="21600" windowHeight="11505" xr2:uid="{67BA941E-2A1D-48F0-9EB1-F75B5C4F512E}"/>
+    <workbookView xWindow="-120" yWindow="330" windowWidth="29040" windowHeight="15990" xr2:uid="{67BA941E-2A1D-48F0-9EB1-F75B5C4F512E}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="124">
   <si>
     <t xml:space="preserve">название места </t>
   </si>
@@ -75,9 +75,6 @@
     <t>Аполлон-11 — американский пилотируемый космический корабль серии «Аполлон», в ходе полёта которого 16—24 июля 1969 года люди впервые в истории совершили посадку на поверхность Луны. 20 июля 1969 года в 20:17:39 UTC командир экипажа Нил Армстронг и пилот Эдвин Олдрин посадили лунный модуль корабля в юго-западном районе Моря Спокойствия. Время пребывания на лунной поверхности составило 21 час 36 минут 21 секунду. Пилот командного модуля Майкл Коллинз всё это время находился на окололунной орбите. Первым человеком, ступившим на Луну, стал Нил Армстронг — это произошло 21 июля в 02:56:15 UTC. Через 15 минут к нему присоединился Олдрин. Астронавты установили в месте посадки флаг США, разместили комплект научных приборов и собрали 21,55 кг образцов лунного грунта, которые были доставлены на Землю. После полёта члены экипажа и образцы лунной породы прошли строгий карантин, не выявивший наличия каких-либо лунных микроорганизмов.</t>
   </si>
   <si>
-    <t>mk1.webp</t>
-  </si>
-  <si>
     <t>Аполлон-11</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
     <t>Луна-2 — вторая советская автоматическая межпланетная станция, первая в мире станция, достигшая поверхности Луны. Это второй аппарат советской космической программы «Луна». 12 сентября 1959 года в 10:39:42 по московскому времени осуществлён пуск ракеты-носителя «Восток-Л», которая вывела станцию на траекторию полёта к Луне. 14 сентября 1959 года в 00:02:24 станция «Луна-2» впервые в мире достигла поверхности Луны в районе Моря Дождей вблизи кратеров Аристилл, Архимед и Автолик</t>
   </si>
   <si>
-    <t>mk2.webp</t>
-  </si>
-  <si>
     <t>mn2.webp</t>
   </si>
   <si>
@@ -109,13 +103,323 @@
   </si>
   <si>
     <t>krL.png</t>
+  </si>
+  <si>
+    <t>mk1.png</t>
+  </si>
+  <si>
+    <t>mk2.png</t>
+  </si>
+  <si>
+    <t>1040;358</t>
+  </si>
+  <si>
+    <t>Аполлон-15</t>
+  </si>
+  <si>
+    <t>Аполлон-17</t>
+  </si>
+  <si>
+    <t>1195;390</t>
+  </si>
+  <si>
+    <t>Аполлон-14</t>
+  </si>
+  <si>
+    <t>920;530</t>
+  </si>
+  <si>
+    <t>Аполлон-16</t>
+  </si>
+  <si>
+    <t>1112;560</t>
+  </si>
+  <si>
+    <t>Аполлон-12 / Сервейер-3</t>
+  </si>
+  <si>
+    <t>888;530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аполлон-15 — девятый пилотируемый космический корабль в рамках программы «Аполлон», четвёртая высадка людей на Луну. Командир экипажа Дэвид Скотт и пилот лунного модуля Джеймс Ирвин провели на Луне почти трое суток (чуть менее 67 часов). Общая продолжительность трёх выходов на лунную поверхность составила 18 ч 30 мин. На Луне экипаж впервые использовал лунный автомобиль, проехав на нём в общей сложности 27,9 км. Было собрано и затем доставлено на Землю 77 килограммов образцов лунного грунта. Космический корабль был впервые оборудован модулем научных приборов и доставил к Луне небольшой искусственный спутник, который был запущен под занавес миссии. На обратном пути к Земле пилот командного модуля Альфред Уорден впервые совершил выход в открытый космос в межпланетном пространстве, чтобы демонтировать и доставить на Землю отснятые фотокассеты.
+</t>
+  </si>
+  <si>
+    <t>Аполлон-16 — десятый пилотируемый полёт в рамках программы «Аполлон», состоявшийся 16–27 апреля 1972 года. Пятая высадка людей на Луну (21 апреля). Первая посадка в горной местности, на плоскогорье неподалёку от кратера Декарт. Это была вторая, после «Аполлона-15», Джей-миссия с акцентом на научные исследования. В распоряжении астронавтов (как и у экипажа предыдущей экспедиции) был лунный автомобиль, «Лунный Ровер № 2». Посадка на Луну едва не была отменена из-за возникших неполадок в резервной системе управления вектором тяги основного двигателя командно-служебного модуля. После тщательного анализа специалистами на Земле сложившейся ситуации и возможных последствий разрешение на посадку было дано с 6-часовой задержкой. Командир экипажа Джон Янг и пилот лунного модуля Чарльз Дьюк провели на Луне почти трое суток — 71 час. Они совершили три поездки на «Лунном Ровере», общей протяжённостью 26,9 километра. Три выхода на поверхность Луны продолжались в общей сложности 20 часов 14 минут. Было собрано и доставлено на Землю 95,7 килограмма образцов лунной породы. В ходе этой экспедиции был установлен рекорд скорости передвижения по Луне на лунном автомобиле — 18 км/ч.</t>
+  </si>
+  <si>
+    <t>Аполлон-17 — космический корабль, на котором состоялся 11-й и последний пилотируемый полёт в рамках программы «Аполлон», в ходе которого была осуществлена шестая высадка людей на Луну. Это была третья Джей-миссия с акцентом на научные исследования. В экипаж корабля впервые вошёл учёный-профессионал, геолог Харрисон Шмитт. В распоряжении астронавтов так же, как и в ходе двух предшествовавших экспедиций, был лунный автомобиль, «Лунный Ровер» № 3. Старт «Аполлона-17» состоялся 7 декабря 1972 года, с задержкой на 2 часа 40 минут. Задержка старта впервые была вызвана неисправностью стартового оборудования. 11 декабря 1972 года «Челленджер» с Юджином Сернаном и Харрисоном Шмиттом на борту совершил посадку в долине Таурус—Литтров, на юго-восточной окраине Моря Ясности. Астронавты оставались на Луне чуть более трёх суток, 74 часа 59 минут 40 секунд. За это время они совершили три выхода из корабля общей продолжительностью 22 часа 3 минуты 57 секунд. Было собрано и привезено на Землю 110,5 кг образцов лунной породы.</t>
+  </si>
+  <si>
+    <t>Аполлон-12 — пилотируемый космический корабль серии «Аполлон», в ходе полёта которого в 1969 году люди второй раз в истории совершили посадку на поверхность Луны. Предусматривалась посадка в Океане Бурь примерно в 1540 км к западу от места посадки корабля «Аполлон-11», сбор образцов лунного грунта, фотографирование на поверхности Луны, установка научных приборов, фотографирование поверхности с селеноцентрической орбиты, поиск автоматического космического аппарата «Сервейер-3» (совершил посадку на Луну 20 апреля 1967 года), демонтаж некоторых деталей указанного аппарата и доставка их на Землю для изучения влияния длительного пребывания в лунных условиях. После успешного прилунения астронавты Чарльз Конрад и Алан Бин достигли аппарата «Сервейер-3». Подойдя к краю кратера, где находился аппарат, астронавты начали спуск. Грунт на склоне оказался прочным и несыпучим, так что подстраховки с помощью верёвки не потребовалось. Подойдя к аппарату, астронавты сообщили, что он имеет не белый цвет, как при старте, а бурый, в то время как грунт вокруг него был серый. Астронавты сфотографировали и осмотрели аппарат и сняли с него около 10 кг деталей, включая телекамеру. Эти предметы были возвращены на Землю для исследований. На обратном пути к лунному модулю астронавты продолжали сбор образцов. Во время второго выхода общая протяжённость маршрута астронавтов составила примерно полтора километра, длительность выхода — 3 часа 54 минуты.</t>
+  </si>
+  <si>
+    <t>Аполлон-14 — пилотируемый космический корабль, на котором была осуществлена третья высадка людей на Луну. Корабль включал в себя командный модуль и лунный модуль. Вес корабля: 44,5 тонны. Для запуска использовалась ракета-носитель «Сатурн-5». Миссии предстояло вернуть доверие к программе «Аполлон» после аварии «Аполлона-13». Общая длительность пребывания лунного модуля на поверхности Луны составила 33 часа 24 минуты. Выход астронавтов на поверхность продолжался 4 часа 29 минут. Астронавты собрали и привезли обратно 23 кг образцов лунной породы.</t>
+  </si>
+  <si>
+    <t>ap15.jpg</t>
+  </si>
+  <si>
+    <t>ap17.jpg</t>
+  </si>
+  <si>
+    <t>ap14.jpg</t>
+  </si>
+  <si>
+    <t>ap16.jpg</t>
+  </si>
+  <si>
+    <t>ap12.jpg</t>
+  </si>
+  <si>
+    <t>Чанъэ-3 / Юйту</t>
+  </si>
+  <si>
+    <t>925;276</t>
+  </si>
+  <si>
+    <t>Луна-17 / Луноход-1</t>
+  </si>
+  <si>
+    <t>820;290</t>
+  </si>
+  <si>
+    <t>Луна-21 / Луноход-2</t>
+  </si>
+  <si>
+    <t>1200;366</t>
+  </si>
+  <si>
+    <t>Луна-23 / 24</t>
+  </si>
+  <si>
+    <t>1375;435</t>
+  </si>
+  <si>
+    <t>Луна-20</t>
+  </si>
+  <si>
+    <t>1345;488</t>
+  </si>
+  <si>
+    <t>Луна-16</t>
+  </si>
+  <si>
+    <t>1345;516</t>
+  </si>
+  <si>
+    <t>Сервейер-6</t>
+  </si>
+  <si>
+    <t>1017;508</t>
+  </si>
+  <si>
+    <t>Сервейер-1</t>
+  </si>
+  <si>
+    <t>777;526</t>
+  </si>
+  <si>
+    <t>Рейнджер-7</t>
+  </si>
+  <si>
+    <t>911;572</t>
+  </si>
+  <si>
+    <t>Сервейер-7</t>
+  </si>
+  <si>
+    <t>965;750</t>
+  </si>
+  <si>
+    <t>ch3.jpg</t>
+  </si>
+  <si>
+    <t>lh1.jpg</t>
+  </si>
+  <si>
+    <t>L21.jpg</t>
+  </si>
+  <si>
+    <t>L24.png</t>
+  </si>
+  <si>
+    <t>L20.jpg</t>
+  </si>
+  <si>
+    <t>L16.webp</t>
+  </si>
+  <si>
+    <t>S6.jpg</t>
+  </si>
+  <si>
+    <t>S1.jpg</t>
+  </si>
+  <si>
+    <t>S7.jpg</t>
+  </si>
+  <si>
+    <t>R7.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сервейер-6 — шестой спускаемый аппарат, запущенный по американской программе «Сервейер» и совершивший мягкую посадку на Луну. «Сервейер-6» прилунился 10 ноября 1967 года в Центральном Заливе. 17 ноября 1967 года аппарат включил двигатели и переместился на новую точку. Этот запуск стал первым в истории, произведённым с поверхности Луны.
+</t>
+  </si>
+  <si>
+    <t>В декабре 2013 года Китай стал второй страной, успешно запустившей луноход «Юйту». Успешная посадка также сделала Китай третьей страной, совершившей мягкую посадку на Луну.</t>
+  </si>
+  <si>
+    <t>Первые колёса на Луне: после высадки с борта «Луны-17» луноход «Луноход-1» в течение следующих 10 месяцев проехал около 10 километров по поверхности Луны. «Луноход-1» стал известен как первый управляемый колёсный аппарат в истории космоса.</t>
+  </si>
+  <si>
+    <t>Второй ровер, который оставил свой след на Луне, — это «Луноход-2» Советского Союза. Он приземлился через месяц после «Аполлона-17» и отправился по холмам и кратерам, преодолев расстояние в 39 километров. Этот рекорд держался до 2014 года, когда марсоход «Opportunity» преодолел на Марсе 40 километров.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Луна-23» — советская автоматическая межпланетная станция для изучения Луны и космического пространства. Посадка на поверхности Луны была осуществлена на юго-восточной окраине Моря Кризисов, однако при этом вертикальная скорость составила 11 м/с при допустимом значении в 5 м/с, наклон станции от вертикали составил 10–15 градусов, что привело к опрокидыванию станции в сторону грунтозаборного устройства и механическому повреждению объекта, разгерметизации приборного отсека. Попытка дать команду с Земли на включение грунтозаборного устройства и подготовку взлётной ступени к старту оказалась безуспешной, поэтому было принято решение провести работу со станцией по сокращённой программе. 9 ноября 1974 года работа со станцией «Луна-23» была прекращена.
+«Луна-24» — последняя советская автоматическая межпланетная станция для изучения Луны, забора и доставки лунного грунта на Землю. Станция была запущена с космодрома Байконур 9 августа 1976 года. В результате анализа результатов этого полёта было впервые получено убедительное доказательство наличия на Луне воды. «Луна-24» доставила на Землю колонку лунного грунта длиной около 160 сантиметров и весом 170 граммов.
+</t>
+  </si>
+  <si>
+    <t>«Луна-20» — советская автоматическая межпланетная станция для изучения Луны и космического пространства. 14 февраля 1972 года осуществлён пуск ракеты-носителя «Протон-К / Д», которая вывела на траекторию полёта к Луне АМС «Луна-20». 21 февраля 1972 года «Луна-20» совершила мягкую посадку на поверхности Луны на участке, примыкающем к северо-восточной оконечности Моря Изобилия. После прилунения станции были переданы на Землю изображения лунной поверхности и произведён забор образцов лунного грунта. Взятые образцы с помощью манипулятора были помещены в контейнер космической ракеты и загерметизированы. 22 февраля 1972 года с поверхности Луны в сторону Земли стартовала взлётная ступень станции «Луна-20». 25 февраля 1972 года на Землю доставлена колонка лунного грунта массой 55 г.</t>
+  </si>
+  <si>
+    <t>«Луна-16» — советская автоматическая межпланетная станция для изучения Луны и космического пространства. 12 сентября 1970 года осуществлён пуск ракеты-носителя «Протон-К/Д», которая вывела на траекторию полёта к Луне АМС «Луна-16», включавшую в себя возвращаемый аппарат. 20 сентября 1970 года в 8:18 станция «Луна-16» совершила мягкую посадку на поверхности Луны в районе Моря Изобилия. Масса опустившейся на Луну станции составила 1880 кг. Затем под управлением и контролем с Земли грунтозаборным устройством посадочной ступени был произведён забор лунного грунта, который в специальной герметичной капсуле был помещён в возвращаемый аппарат. 21 сентября 1970 года в 10:43 с поверхности Луны стартовала ракета «Луна — Земля» с возвращаемым аппаратом автоматической межпланетной станции «Луна-16», при этом двигатель ракеты работал до тех пор, пока скорость аппарата не достигла значения 2,708 км/сек. Масса стартовавшей ступени была 512 кг. 24 сентября 1970 года в 4:50 возвращаемый аппарат станции «Луна-16» массой 35 кг был отделён от ракеты «Луна — Земля», в 8:10 он вошёл в атмосферу Земли, на высоте 14,5 км раскрылся тормозной парашют, который отделился на высоте 11 км, при этом раскрылся основной парашют, и в 8:26 возвращаемый аппарат совершил мягкую посадку на территории СССР в 80 километрах юго-восточнее города Джезказган в Казахстане. Общая масса колонки грунта, доставленной на Землю, составила 101 грамм. «Луна-16» стала первым автоматическим аппаратом, доставившим внеземное вещество на Землю.</t>
+  </si>
+  <si>
+    <t>«Сервейер-1» — первый американский спускаемый аппарат, совершивший мягкую посадку на небесное тело, а именно на Луну. Является частью лунной программы «Сервейер» по запуску беспилотных спускаемых аппаратов с целью изучения Луны с её поверхности. После мягкой посадки на Луну аппарат начал собирать данные, необходимые для подготовки к полётам миссии «Аполлон». «Сервейер-1» успешно прилунился 2 июня 1966 года в Океане Бурь, тем самым став первым американским спускаемым аппаратом, который совершил мягкую посадку на небесное тело. За 4 месяца до этого на Луну успешно прилунился советский спускаемый аппарат «Луна-9».</t>
+  </si>
+  <si>
+    <t>«Рейнджер-7» — американская автоматическая межпланетная станция для изучения Луны; первый американский зонд, передавший на Землю изображения Луны, сделанные с близкого расстояния; первый полностью успешный полёт по программе «Рейнджер». Целью полёта «Рейнджера-7» было достижение поверхности Луны и передача чётких фотографий лунной поверхности в последние минуты полёта перед столкновением. Никаких других экспериментов программой полёта не подразумевалось.</t>
+  </si>
+  <si>
+    <t>«Сервейер-7» — седьмая и последняя автоматическая лунная станция НАСА, запущенная по программе «Сервейер». Стартовал 7 января 1968 года, прилунился 10 января того же года в 25,6 км к северу от кратера Тихо. «Сервейер-7» передал на Землю 21 091 изображение лунной поверхности.</t>
+  </si>
+  <si>
+    <t>699;428</t>
+  </si>
+  <si>
+    <t>962;759</t>
+  </si>
+  <si>
+    <t>Кратер Тихо</t>
+  </si>
+  <si>
+    <t>Лавовая трубка в Холмах Мариуса</t>
+  </si>
+  <si>
+    <t>1760;626</t>
+  </si>
+  <si>
+    <t>Кратер Циолковский</t>
+  </si>
+  <si>
+    <t>1710;481</t>
+  </si>
+  <si>
+    <t>Кратер Кинг</t>
+  </si>
+  <si>
+    <t>Кратер Страттон</t>
+  </si>
+  <si>
+    <t>1963;544</t>
+  </si>
+  <si>
+    <t>Кратер Ван де Грааф</t>
+  </si>
+  <si>
+    <t>2005;663</t>
+  </si>
+  <si>
+    <t>Кратер Апполон</t>
+  </si>
+  <si>
+    <t>166;712</t>
+  </si>
+  <si>
+    <t>56;820</t>
+  </si>
+  <si>
+    <t>Бассейн Южный полюс — Эйткен</t>
+  </si>
+  <si>
+    <t>Кратер Герцшпрунг</t>
+  </si>
+  <si>
+    <t>298;509</t>
+  </si>
+  <si>
+    <t>488;617</t>
+  </si>
+  <si>
+    <t>Море Восточное</t>
+  </si>
+  <si>
+    <t>Бассейн Южный полюс — Эйткен — самый большой кратер Луны. Расположен на юге обратной стороны. Имеет размер 2400×2050 км, что делает его одним из крупнейших кратеров Солнечной системы. Это глубочайшая и старейшая известная ударная структура Луны. Глубина бассейна достигает 8 км, а полный интервал высот (от глубочайших точек дна до высочайших точек вала) составляет 16,1 км. Его край виден с Земли как горная цепь, расположенная у южного лимба Луны («горы Лейбница»). Поверхность бассейна выделяется тёмным цветом. Бассейн назван по именам двух объектов на его противоположных сторонах: южного полюса Луны и кратера Эйткен. В пределах бассейна находится самая низкая точка поверхности Луны (−8,81 км относительно среднего уровня, на дне маленького безымянного кратера в кратере Антониади), а на его северо-восточном краю — очень высокая местность (+8,16 км, около кратера Доплер). Толщина лунной коры в области бассейна меньше обычной: в центральной части — около 30 км, тогда как в окрестностях — 60–80 км (средняя толщина коры Луны — около 50 км). Возраст бассейна оценивается в 4,2–4,3 млрд лет. Он образовался вследствие удара огромной силы.</t>
+  </si>
+  <si>
+    <t>Аполлон — гигантский древний ударный кратер, неофициально именуемый бассейном Аполлон, в южном полушарии обратной стороны Луны. Находится внутри бассейна Южный полюс — Эйткен. Название присвоено в честь американской космической программы «Аполлон». Образование кратера относится к донектарскому периоду. Кратер имеет двойной вал, причём диаметр внутреннего вала в два раза меньше диаметра внешнего вала. Оба вала подверглись значительному разрушению за время существования кратера и теперь представляют собой нерегулярное скопление дугообразных участков гор. Многие участки кратера затоплены лавой и имеют более низкое альбедо по сравнению с окружающей местностью. Наибольшие по площади такие участки находятся в центре кратера и в его южной части. Возраст лавовых потоков определён от 2,49 до 3,51 млрд лет в центральной и северной части кратера и около 2,44 млрд лет в южной части кратера.</t>
+  </si>
+  <si>
+    <t>Кратер Герцшпрунг — огромный кратер в экваториальной области обратной стороны Луны, один из крупнейших лунных кратеров. Диаметр — 570 км. Носит имя датского астронома Эйнара Герцшпрунга. По размерам Герцшпрунг превышает некоторые лунные моря видимой стороны, однако лишь небольшая часть его площади покрыта лавой. Это талассоид — ударный бассейн, не заполненный тёмной лавой. Кратер образовался в нектарском периоде в результате падения крупного астероида. Он представляет собой многокольцевую впадину: чётко выражены два кольца — 570 км в диаметре (основное) и 270 км (внутреннее). Средняя глубина Герцшпрунга — 4,50 км, высота вала — 1,06 км. В пределах внутреннего кольца поверхность более гладкая и молодая, что указывает на её покрытие лавой, излившейся значительно позже образования кратера. С кратером связана отрицательная гравитационная аномалия (понижение ускорения свободного падения на 45 мГал). Герцшпрунг существенно разрушен последующими ударами: его вал на северо-востоке перекрыт 120-километровым кратером Майкельсон, а на западе — 100-километровым кратером Вавилов. Кратер покрыт выбросами от удара, образовавшего бассейн Моря Восточного; на нём много вторичных кратеров этого бассейна.</t>
+  </si>
+  <si>
+    <t>Кратер Ван де Грааф — крупный ударный кратер необычной неправильной формы в виде двух соединённых кратеров («восьмёрки»), находящийся на обратной стороне Луны на северо-восточной границе Моря Мечты. Образование кратера относится к нектарскому периоду. Назван в честь американского физика Роберта ван де Граафа (1901—1967). Кратер образовался 3,92–4,5 млрд лет назад. Вероятнее всего, причиной его появления являются два одновременных импакта, при этом взаимодействие выброшенного материала привело к тому, что перемычка между двумя кратерами в центральной части структуры не сформировалась. Кратер является антиподом бассейна Моря Дождей; необычная структура внутренней части вала может объясняться воздействием сейсмических волн, достигших обратной стороны Луны при имбрийском импакте. В кратере Ван де Грааф обнаружена магнитная аномалия, вероятно, связанная с вихреобразной геологической структурой. Кроме того, в кратере зарегистрирован уровень радиоактивности несколько выше характерного фона лунной поверхности, в основном за счёт повышенного содержания тория в породах KREEP.</t>
+  </si>
+  <si>
+    <t>Кратер Страттон — большой древний ударный кратер в экваториальной области обратной стороны Луны. Название присвоено в честь английского астронома Фредерика Стрэттона (1881—1960). Образование кратера относится к нектарскому периоду. Кратер Страттон имеет близкую к циркулярной форму с небольшим выступом в южной части и значительно разрушен. Вал сглажен, юго-западная часть вала перекрыта сателлитным кратером Страттон Q. Внутренний склон кратера широкий, отмечен множеством мелких кратеров. Высота вала над окружающей местностью достигает 1290 м. Дно чаши кратера относительно ровное, с отдельными невысокими холмами. Небольшой округлый центральный пик несколько смещён к юго-востоку от центра чаши.</t>
+  </si>
+  <si>
+    <t>Циолковский — кратер на обратной стороне Луны. Расположен в южном полушарии к западу от кратера Гагарин. Своё имя кратер получил в честь Константина Эдуардовича Циолковского, основоположника теории межпланетных сообщений. Среди десятков тысяч лунных кратеров Циолковский является одним из самых эффектных: он обладает высокими террасами и чётким внешним валом. Дно кратера очень тёмное, так как внутри него расположено озеро застывшей чёрной лавы, в центре которого ярким пятном выделяется центральная горка. На обратной стороне Луны нет обширных тёмных равнин — лунных морей, поскольку из-за приливных сил кора там почти в два раза толще, чем на видимой стороне, и магме было трудно пробиться из недр на поверхность. Однако в районе кратера Циолковский толщина лунной коры достигает рекордной величины — 75 километров. Удар метеорита, сформировавшего этот кратер, был особенно сильным: трещины под кратером проникли чрезвычайно глубоко в лунные недра, достигнув слоя магмы. Базальтовый расплав излился на поверхность и наполовину затопил чашу кратера, образовав после застывания чёрную равнину. Диаметр кратера — 180 км. Он служит отличным ориентиром на лунных картах и при полётах вокруг Луны космических аппаратов.</t>
+  </si>
+  <si>
+    <t>Кратер Кинг — большой ударный кратер в экваториальной области обратной стороны Луны. Название присвоено в честь американского физика и астрофизика Артура Скотта Кинга (1876—1957) и американского астронома Эдварда Скинера Кинга (1861—1931). Образование кратера относится к коперниковскому периоду. Кратер Кинг имеет полигональную форму и незначительные разрушения. Это один из самых молодых кратеров на обратной стороне Луны. Вал кратера несколько хуже сформирован в северной части и имеет здесь меньшую высоту. В юго-восточной части вала имеется впадина, образованная массивным обрушением пород. Внутренний склон вала имеет террасовидную структуру, особенно хорошо различимую в восточной части; у подножия склона находятся осыпи пород. Высота вала над окружающей местностью около 1330 м. В чаше кратера и за её пределами (к северу от кратера) находятся массивы пород, выброшенных в расплавленном состоянии и затвердевших по мере остывания. Кратер Кинг окружён системой ярких лучей. 11 октября 1967 года приблизительно в 40 км на юго-западе от вала кратера Кинг, после окончания программы своей работы, совершил жёсткую посадку зонд «Lunar Orbiter-II».</t>
+  </si>
+  <si>
+    <t>Кратер Тихо — 85-километровый ударный кратер на Луне, в южной части видимой стороны. Назван в честь датского астронома и алхимика XVI века Тихо Браге. Это один из наиболее интересных лунных кратеров: он окружён самой заметной на Луне системой светлых лучей, простирающихся на тысячи километров. Особенно хорошо они видны в полнолуние, но различимы и тогда, когда освещены только светом Земли. Окрестности Тихо усеяны множеством других кратеров разных размеров. Некоторые из них являются вторичными (образованы телами, выброшенными при ударе, создавшем Тихо).</t>
+  </si>
+  <si>
+    <t>Лавовые трубки — каналы, образующиеся при неравномерном остывании текущей со склонов вулкана лавы. Гигантские провалы в лунной поверхности — это обрушившиеся своды лавовых трубок, свидетельствующие о древней вулканической активности. В лавовых трубках Луны уже в паре метров от поверхности круглосуточно и круглогодично держится температура от –30 до –40 °C. Снаружи температура колеблется от –150 °C (ночью) до +100 °C (в местный лунный полдень). Предполагается, что в таких трубках может присутствовать вода. Эти условия рассматриваются как предпочтительные для возможной жизнедеятельности человека и промышленных операций. Сооружение лунных баз внутри лавовых трубок может дать функциональные, технические и экономические преимущества.</t>
+  </si>
+  <si>
+    <t>Море Восточное — лунное море, расположенное на западной окраине видимого с Земли полушария Луны. Море Восточное лежит в многокольцевом ударном бассейне — гигантском кратере, образовавшемся от удара астероида. Диаметр основного кольца этого бассейна составляет около 930 км. В отличие от бассейнов большинства других лунных морей, бассейн Моря Восточного слабо заполнен застывшей базальтовой лавой, что позволяет наблюдать его морфологическую структуру. Центральная часть моря сложена тонким слоем базальтов — предположительно менее 1 км в толщину, то есть менее мощным, чем у других лунных морей на видимом полушарии. Столкновение, приведшее к возникновению бассейна моря, вызвало появление трёх концентрических складчатостей на лунной коре. Внутренняя гряда этого огромного ударного кратера сформирована горами Рук, внешнюю цепь диаметром 930 км образуют горы Кордильеры. Выброшенная в результате столкновения горная порода имеет грубую булыжниковую структуру, начинается у внешних склонов Кордильер и простирается до 500 км в разные стороны, формируя линейные лучевые образования, сходящиеся к центру моря. На противоположной морю точке лунной поверхности расположено Море Краевое. В бассейне Моря Восточного лежит также Озеро Весны, рассматриваемое как одно из возможных мест для строительства лунной базы.</t>
+  </si>
+  <si>
+    <t>lt.jpg</t>
+  </si>
+  <si>
+    <t>kt.jpg</t>
+  </si>
+  <si>
+    <t>kc.jpg</t>
+  </si>
+  <si>
+    <t>kk.png</t>
+  </si>
+  <si>
+    <t>ks.jpg</t>
+  </si>
+  <si>
+    <t>kv.jpg</t>
+  </si>
+  <si>
+    <t>ka.png</t>
+  </si>
+  <si>
+    <t>bs.jpg</t>
+  </si>
+  <si>
+    <t>kg.jpg</t>
+  </si>
+  <si>
+    <t>mv.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,6 +427,13 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -145,8 +456,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -461,12 +782,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{602C8880-9636-4FA4-818D-7C4189108CCC}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
     <col min="2" max="3" width="19.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
     <col min="5" max="5" width="13.140625" customWidth="1"/>
     <col min="6" max="6" width="39.42578125" customWidth="1"/>
     <col min="7" max="7" width="10.140625" customWidth="1"/>
@@ -492,9 +813,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -502,57 +823,585 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
         <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E27" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D38" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\motifoye\Desktop\map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733F7FFB-902B-4B42-B9E0-1CCF59B8A96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45053E7-D606-44EB-9C91-339E59548781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4365" yWindow="6045" windowWidth="21600" windowHeight="11505" xr2:uid="{67BA941E-2A1D-48F0-9EB1-F75B5C4F512E}"/>
+    <workbookView xWindow="-120" yWindow="330" windowWidth="29040" windowHeight="15990" xr2:uid="{67BA941E-2A1D-48F0-9EB1-F75B5C4F512E}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -99,9 +99,6 @@
     <t>mk3.png</t>
   </si>
   <si>
-    <t>krL.png</t>
-  </si>
-  <si>
     <t>mk1.png</t>
   </si>
   <si>
@@ -160,9 +157,6 @@
     <t>ap17.jpg</t>
   </si>
   <si>
-    <t>ap12.jpg</t>
-  </si>
-  <si>
     <t>Чанъэ-3 / Юйту</t>
   </si>
   <si>
@@ -224,9 +218,6 @@
   </si>
   <si>
     <t>ch3.jpg</t>
-  </si>
-  <si>
-    <t>lh1.jpg</t>
   </si>
   <si>
     <t>L21.jpg</t>
@@ -403,9 +394,6 @@
     <t>mv.png</t>
   </si>
   <si>
-    <t>ap11.jpg;i.webp</t>
-  </si>
-  <si>
     <t>ap16.jpg;2ap16.jpg</t>
   </si>
   <si>
@@ -413,6 +401,18 @@
   </si>
   <si>
     <t>R7.webp;r7.jpg</t>
+  </si>
+  <si>
+    <t>lh1.jpg;mr.webp</t>
+  </si>
+  <si>
+    <t>ap12.jpg;ap122.webp;ap123.jpg</t>
+  </si>
+  <si>
+    <t>krL.png;kl2.jpg;kl3.png</t>
+  </si>
+  <si>
+    <t>ap11.jpg</t>
   </si>
 </sst>
 </file>
@@ -821,13 +821,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
         <v>6</v>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
@@ -861,7 +861,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
@@ -875,19 +875,19 @@
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
@@ -895,19 +895,19 @@
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
         <v>6</v>
@@ -915,19 +915,19 @@
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" t="s">
         <v>6</v>
@@ -935,19 +935,19 @@
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8" t="s">
         <v>6</v>
@@ -955,19 +955,19 @@
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
         <v>31</v>
       </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
         <v>6</v>
@@ -975,19 +975,19 @@
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
         <v>7</v>
@@ -995,19 +995,19 @@
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11" t="s">
         <v>7</v>
@@ -1015,19 +1015,19 @@
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
         <v>7</v>
@@ -1035,19 +1035,19 @@
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -1055,19 +1055,19 @@
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -1075,19 +1075,19 @@
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" t="s">
         <v>7</v>
@@ -1095,19 +1095,19 @@
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16" t="s">
         <v>7</v>
@@ -1115,19 +1115,19 @@
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
         <v>7</v>
@@ -1135,19 +1135,19 @@
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
         <v>7</v>
@@ -1155,19 +1155,19 @@
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
         <v>7</v>
@@ -1175,16 +1175,16 @@
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -1195,16 +1195,16 @@
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
@@ -1215,16 +1215,16 @@
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
@@ -1235,16 +1235,16 @@
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
@@ -1255,16 +1255,16 @@
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
@@ -1275,16 +1275,16 @@
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
@@ -1295,16 +1295,16 @@
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
@@ -1315,16 +1315,16 @@
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
@@ -1335,16 +1335,16 @@
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
@@ -1355,16 +1355,16 @@
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
